--- a/Config/Tables/背包.xlsx
+++ b/Config/Tables/背包.xlsx
@@ -28,13 +28,304 @@
     <x:t>售价</x:t>
   </x:si>
   <x:si>
-    <x:t>木剑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>治疗药水</x:t>
-  </x:si>
-  <x:si>
-    <x:t>皮甲</x:t>
+    <x:t>末行·改</x:t>
+  </x:si>
+  <x:si>
+    <x:t>治疗药水·1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>皮甲·1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>铁剑·1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>法杖·1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>布靴·1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>护符·1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>卷轴·1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>矿石·1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>药草·1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>木剑·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>治疗药水·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>皮甲·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>铁剑·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>法杖·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>布靴·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>护符·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>卷轴·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>矿石·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>药草·2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>木剑·3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>治疗药水·3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>皮甲·3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>铁剑·3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>法杖·3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>布靴·3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>护符·3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>卷轴·3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>矿石·3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>药草·3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>木剑·4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>治疗药水·4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>皮甲·4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>铁剑·4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>法杖·4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>布靴·4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>护符·4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>卷轴·4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>矿石·4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>药草·4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>木剑·5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>治疗药水·5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>皮甲·5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>铁剑·5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>法杖·5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>布靴·5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>护符·5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>卷轴·5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>矿石·5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>药草·5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>木剑·6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>治疗药水·6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>皮甲·6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>铁剑·6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>法杖·6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>布靴·6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>护符·6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>卷轴·6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>矿石·6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>药草·6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>木剑·7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>治疗药水·7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>皮甲·7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>铁剑·7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>法杖·7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>布靴·7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>护符·7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>卷轴·7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>矿石·7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>药草·7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>木剑·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>治疗药水·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>皮甲·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>铁剑·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>法杖·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>布靴·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>护符·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>卷轴·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>矿石·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>药草·8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>木剑·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>治疗药水·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>皮甲·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>铁剑·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>法杖·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>布靴·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>护符·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>卷轴·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>矿石·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>药草·9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>木剑·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>治疗药水·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>皮甲·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>铁剑·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>法杖·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>布靴·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>护符·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>卷轴·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>矿石·10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>首行·改</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -405,7 +696,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D4"/>
+  <x:dimension ref="A1:D101"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -427,13 +718,13 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>25</x:v>
+        <x:v>1234</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
@@ -447,7 +738,7 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>10</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
@@ -458,10 +749,1368 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>1</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D4" s="0">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:4">
+      <x:c r="A5" s="0">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C5" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" s="0">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:4">
+      <x:c r="A6" s="0">
+        <x:v>1005</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C6" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D6" s="0">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:4">
+      <x:c r="A7" s="0">
+        <x:v>1006</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C7" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D7" s="0">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:4">
+      <x:c r="A8" s="0">
+        <x:v>1007</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C8" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D8" s="0">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:4">
+      <x:c r="A9" s="0">
+        <x:v>1008</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C9" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D9" s="0">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:4">
+      <x:c r="A10" s="0">
+        <x:v>1009</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D10" s="0">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:4">
+      <x:c r="A11" s="0">
+        <x:v>1010</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D11" s="0">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:4">
+      <x:c r="A12" s="0">
+        <x:v>1011</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D12" s="0">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:4">
+      <x:c r="A13" s="0">
+        <x:v>1012</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D13" s="0">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:4">
+      <x:c r="A14" s="0">
+        <x:v>1013</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C14" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D14" s="0">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:4">
+      <x:c r="A15" s="0">
+        <x:v>1014</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C15" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D15" s="0">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:4">
+      <x:c r="A16" s="0">
+        <x:v>1015</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C16" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D16" s="0">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:4">
+      <x:c r="A17" s="0">
+        <x:v>1016</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C17" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D17" s="0">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:4">
+      <x:c r="A18" s="0">
+        <x:v>1017</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D18" s="0">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:4">
+      <x:c r="A19" s="0">
+        <x:v>1018</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C19" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D19" s="0">
+        <x:v>129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:4">
+      <x:c r="A20" s="0">
+        <x:v>1019</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C20" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D20" s="0">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:4">
+      <x:c r="A21" s="0">
+        <x:v>1020</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C21" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D21" s="0">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:4">
+      <x:c r="A22" s="0">
+        <x:v>1021</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C22" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D22" s="0">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:4">
+      <x:c r="A23" s="0">
+        <x:v>1022</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C23" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D23" s="0">
+        <x:v>157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:4">
+      <x:c r="A24" s="0">
+        <x:v>1023</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C24" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D24" s="0">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:4">
+      <x:c r="A25" s="0">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C25" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D25" s="0">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:4">
+      <x:c r="A26" s="0">
+        <x:v>1025</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C26" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D26" s="0">
+        <x:v>178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:4">
+      <x:c r="A27" s="0">
+        <x:v>1026</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C27" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D27" s="0">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:4">
+      <x:c r="A28" s="0">
+        <x:v>1027</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C28" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D28" s="0">
+        <x:v>192</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:4">
+      <x:c r="A29" s="0">
+        <x:v>1028</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C29" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D29" s="0">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:4">
+      <x:c r="A30" s="0">
+        <x:v>1029</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C30" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D30" s="0">
+        <x:v>206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:4">
+      <x:c r="A31" s="0">
+        <x:v>1030</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C31" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D31" s="0">
+        <x:v>213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:4">
+      <x:c r="A32" s="0">
+        <x:v>1031</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C32" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D32" s="0">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:4">
+      <x:c r="A33" s="0">
+        <x:v>1032</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C33" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D33" s="0">
+        <x:v>227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:4">
+      <x:c r="A34" s="0">
+        <x:v>1033</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D34" s="0">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:4">
+      <x:c r="A35" s="0">
+        <x:v>1034</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C35" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D35" s="0">
+        <x:v>241</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:4">
+      <x:c r="A36" s="0">
+        <x:v>1035</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C36" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D36" s="0">
+        <x:v>248</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:4">
+      <x:c r="A37" s="0">
+        <x:v>1036</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C37" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D37" s="0">
+        <x:v>255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:4">
+      <x:c r="A38" s="0">
+        <x:v>1037</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C38" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D38" s="0">
+        <x:v>262</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:4">
+      <x:c r="A39" s="0">
+        <x:v>1038</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C39" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D39" s="0">
+        <x:v>269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:4">
+      <x:c r="A40" s="0">
+        <x:v>1039</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C40" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D40" s="0">
+        <x:v>276</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:4">
+      <x:c r="A41" s="0">
+        <x:v>1040</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C41" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D41" s="0">
+        <x:v>283</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:4">
+      <x:c r="A42" s="0">
+        <x:v>1041</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C42" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D42" s="0">
+        <x:v>290</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:4">
+      <x:c r="A43" s="0">
+        <x:v>1042</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C43" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D43" s="0">
+        <x:v>297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:4">
+      <x:c r="A44" s="0">
+        <x:v>1043</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C44" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D44" s="0">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:4">
+      <x:c r="A45" s="0">
+        <x:v>1044</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C45" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D45" s="0">
+        <x:v>311</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:4">
+      <x:c r="A46" s="0">
+        <x:v>1045</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C46" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D46" s="0">
+        <x:v>318</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:4">
+      <x:c r="A47" s="0">
+        <x:v>1046</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C47" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D47" s="0">
+        <x:v>325</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:4">
+      <x:c r="A48" s="0">
+        <x:v>1047</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C48" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D48" s="0">
+        <x:v>332</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:4">
+      <x:c r="A49" s="0">
+        <x:v>1048</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C49" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D49" s="0">
+        <x:v>339</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:4">
+      <x:c r="A50" s="0">
+        <x:v>1049</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C50" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D50" s="0">
+        <x:v>346</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:4">
+      <x:c r="A51" s="0">
+        <x:v>1050</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C51" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D51" s="0">
+        <x:v>353</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:4">
+      <x:c r="A52" s="0">
+        <x:v>1051</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C52" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D52" s="0">
+        <x:v>360</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:4">
+      <x:c r="A53" s="0">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C53" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D53" s="0">
+        <x:v>367</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:4">
+      <x:c r="A54" s="0">
+        <x:v>1053</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C54" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D54" s="0">
+        <x:v>374</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:4">
+      <x:c r="A55" s="0">
+        <x:v>1054</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C55" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D55" s="0">
+        <x:v>381</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:4">
+      <x:c r="A56" s="0">
+        <x:v>1055</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C56" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D56" s="0">
+        <x:v>388</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:4">
+      <x:c r="A57" s="0">
+        <x:v>1056</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C57" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D57" s="0">
+        <x:v>395</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:4">
+      <x:c r="A58" s="0">
+        <x:v>1057</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
         <x:v>60</x:v>
+      </x:c>
+      <x:c r="C58" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D58" s="0">
+        <x:v>402</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:4">
+      <x:c r="A59" s="0">
+        <x:v>1058</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C59" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D59" s="0">
+        <x:v>409</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:4">
+      <x:c r="A60" s="0">
+        <x:v>1059</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C60" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D60" s="0">
+        <x:v>416</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:4">
+      <x:c r="A61" s="0">
+        <x:v>1060</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C61" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D61" s="0">
+        <x:v>423</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:4">
+      <x:c r="A62" s="0">
+        <x:v>1061</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C62" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D62" s="0">
+        <x:v>430</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:4">
+      <x:c r="A63" s="0">
+        <x:v>1062</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C63" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D63" s="0">
+        <x:v>437</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:4">
+      <x:c r="A64" s="0">
+        <x:v>1063</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C64" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D64" s="0">
+        <x:v>444</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:4">
+      <x:c r="A65" s="0">
+        <x:v>1064</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C65" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D65" s="0">
+        <x:v>451</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:4">
+      <x:c r="A66" s="0">
+        <x:v>1065</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C66" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D66" s="0">
+        <x:v>458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:4">
+      <x:c r="A67" s="0">
+        <x:v>1066</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C67" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D67" s="0">
+        <x:v>465</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:4">
+      <x:c r="A68" s="0">
+        <x:v>1067</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C68" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D68" s="0">
+        <x:v>472</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:4">
+      <x:c r="A69" s="0">
+        <x:v>1068</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C69" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D69" s="0">
+        <x:v>479</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:4">
+      <x:c r="A70" s="0">
+        <x:v>1069</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C70" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D70" s="0">
+        <x:v>486</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:4">
+      <x:c r="A71" s="0">
+        <x:v>1070</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C71" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D71" s="0">
+        <x:v>493</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:4">
+      <x:c r="A72" s="0">
+        <x:v>1071</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C72" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D72" s="0">
+        <x:v>500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:4">
+      <x:c r="A73" s="0">
+        <x:v>1072</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C73" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D73" s="0">
+        <x:v>507</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:4">
+      <x:c r="A74" s="0">
+        <x:v>1073</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C74" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D74" s="0">
+        <x:v>514</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:4">
+      <x:c r="A75" s="0">
+        <x:v>1074</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C75" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D75" s="0">
+        <x:v>521</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:4">
+      <x:c r="A76" s="0">
+        <x:v>1075</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C76" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D76" s="0">
+        <x:v>528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:4">
+      <x:c r="A77" s="0">
+        <x:v>1076</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C77" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D77" s="0">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:4">
+      <x:c r="A78" s="0">
+        <x:v>1077</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C78" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D78" s="0">
+        <x:v>542</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:4">
+      <x:c r="A79" s="0">
+        <x:v>1078</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C79" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D79" s="0">
+        <x:v>549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:4">
+      <x:c r="A80" s="0">
+        <x:v>1079</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C80" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D80" s="0">
+        <x:v>556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:4">
+      <x:c r="A81" s="0">
+        <x:v>1080</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C81" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D81" s="0">
+        <x:v>563</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:4">
+      <x:c r="A82" s="0">
+        <x:v>1081</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C82" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D82" s="0">
+        <x:v>570</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:4">
+      <x:c r="A83" s="0">
+        <x:v>1082</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C83" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D83" s="0">
+        <x:v>577</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:4">
+      <x:c r="A84" s="0">
+        <x:v>1083</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C84" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D84" s="0">
+        <x:v>584</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:4">
+      <x:c r="A85" s="0">
+        <x:v>1084</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C85" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D85" s="0">
+        <x:v>591</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:4">
+      <x:c r="A86" s="0">
+        <x:v>1085</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C86" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D86" s="0">
+        <x:v>598</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:4">
+      <x:c r="A87" s="0">
+        <x:v>1086</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C87" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D87" s="0">
+        <x:v>605</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:4">
+      <x:c r="A88" s="0">
+        <x:v>1087</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C88" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D88" s="0">
+        <x:v>612</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:4">
+      <x:c r="A89" s="0">
+        <x:v>1088</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C89" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D89" s="0">
+        <x:v>619</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:4">
+      <x:c r="A90" s="0">
+        <x:v>1089</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C90" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D90" s="0">
+        <x:v>626</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:4">
+      <x:c r="A91" s="0">
+        <x:v>1090</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C91" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D91" s="0">
+        <x:v>633</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:4">
+      <x:c r="A92" s="0">
+        <x:v>1091</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C92" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D92" s="0">
+        <x:v>640</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:4">
+      <x:c r="A93" s="0">
+        <x:v>1092</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C93" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D93" s="0">
+        <x:v>647</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:4">
+      <x:c r="A94" s="0">
+        <x:v>1093</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C94" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D94" s="0">
+        <x:v>654</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:4">
+      <x:c r="A95" s="0">
+        <x:v>1094</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C95" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D95" s="0">
+        <x:v>661</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:4">
+      <x:c r="A96" s="0">
+        <x:v>1095</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C96" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D96" s="0">
+        <x:v>668</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:4">
+      <x:c r="A97" s="0">
+        <x:v>1096</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C97" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D97" s="0">
+        <x:v>675</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:4">
+      <x:c r="A98" s="0">
+        <x:v>1097</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C98" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D98" s="0">
+        <x:v>682</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:4">
+      <x:c r="A99" s="0">
+        <x:v>1098</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C99" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D99" s="0">
+        <x:v>689</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:4">
+      <x:c r="A100" s="0">
+        <x:v>1099</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C100" s="0">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D100" s="0">
+        <x:v>696</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:4">
+      <x:c r="A101" s="0">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C101" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D101" s="0">
+        <x:v>4321</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
